--- a/Lab/Programme.json_builder/work/tableau_ingest.xlsx
+++ b/Lab/Programme.json_builder/work/tableau_ingest.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -475,17 +475,17 @@
     <row r="2" ht="40" customHeight="1">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>La vie après Siham - VOST</t>
+          <t>Les échos du passé - VOST</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr"/>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>ME</t>
         </is>
       </c>
       <c r="D2" s="5" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
@@ -496,7 +496,7 @@
     <row r="3" ht="40" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Baise-en-ville</t>
+          <t>CM1 - Votre attention s'il-vous-plait</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr"/>
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="D3" s="5" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
@@ -517,28 +517,28 @@
     <row r="4" ht="40" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>La pire mère au monde</t>
+          <t>Christy and his brother - VOST + CM1</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr"/>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>VE</t>
+          <t>JE</t>
         </is>
       </c>
       <c r="D4" s="5" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>15h</t>
+          <t>21h</t>
         </is>
       </c>
     </row>
     <row r="5" ht="40" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Victor comme tout le monde</t>
+          <t>Ma frère</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr"/>
@@ -548,39 +548,39 @@
         </is>
       </c>
       <c r="D5" s="5" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>21h</t>
+          <t>15h</t>
         </is>
       </c>
     </row>
     <row r="6" ht="40" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Le grand Phuket - VOST</t>
+          <t>Hamnet - VOST</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr"/>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>VE</t>
         </is>
       </c>
       <c r="D6" s="5" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>15h</t>
+          <t>21h</t>
         </is>
       </c>
     </row>
     <row r="7" ht="40" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>En route</t>
+          <t>Olivia</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr"/>
@@ -590,18 +590,18 @@
         </is>
       </c>
       <c r="D7" s="5" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>17h</t>
+          <t>16h</t>
         </is>
       </c>
     </row>
     <row r="8" ht="40" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Urchin - VOST</t>
+          <t>Bardot</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr"/>
@@ -611,7 +611,7 @@
         </is>
       </c>
       <c r="D8" s="5" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
@@ -622,7 +622,7 @@
     <row r="9" ht="40" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Noise - VOST</t>
+          <t>Grand ciel</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr"/>
@@ -632,18 +632,18 @@
         </is>
       </c>
       <c r="D9" s="5" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>21h15</t>
+          <t>21h</t>
         </is>
       </c>
     </row>
     <row r="10" ht="40" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Les fleurs du manguier - VOST</t>
+          <t>Biscuit le chien fantastique</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr"/>
@@ -653,18 +653,18 @@
         </is>
       </c>
       <c r="D10" s="5" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>11h</t>
+          <t>15h</t>
         </is>
       </c>
     </row>
     <row r="11" ht="40" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Sauvage</t>
+          <t>L'affaire Bojarski</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr"/>
@@ -674,39 +674,39 @@
         </is>
       </c>
       <c r="D11" s="5" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>15h</t>
+          <t>17h</t>
         </is>
       </c>
     </row>
     <row r="12" ht="40" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>I swear - VOST</t>
+          <t>Tafiti</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr"/>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>DI</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="D12" s="5" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>17h</t>
+          <t>16h</t>
         </is>
       </c>
     </row>
     <row r="13" ht="40" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Ma frère</t>
+          <t>Le mage du Kremlin - VOST</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr"/>
@@ -716,7 +716,7 @@
         </is>
       </c>
       <c r="D13" s="5" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
     <row r="14" ht="40" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Tatouage - VOST</t>
+          <t>The mastermind - VOST</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr"/>
@@ -737,7 +737,7 @@
         </is>
       </c>
       <c r="D14" s="5" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
@@ -748,7 +748,7 @@
     <row r="15" ht="40" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>A pied d'œuvre</t>
+          <t>Avatar De cendres et de feu</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr"/>
@@ -758,39 +758,39 @@
         </is>
       </c>
       <c r="D15" s="5" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>21h</t>
+          <t>16h</t>
         </is>
       </c>
     </row>
     <row r="16" ht="40" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Alter ego</t>
+          <t>En garde - VOST</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr"/>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>VE</t>
+          <t>JE</t>
         </is>
       </c>
       <c r="D16" s="5" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>19h</t>
+          <t>21h</t>
         </is>
       </c>
     </row>
     <row r="17" ht="40" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Le mystérieux regard du flamant rose - VOST</t>
+          <t>CM2 - Réel</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr"/>
@@ -800,39 +800,39 @@
         </is>
       </c>
       <c r="D17" s="5" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>21h15</t>
+          <t>21h</t>
         </is>
       </c>
     </row>
     <row r="18" ht="40" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>Un jour avec mon père - VOST</t>
+          <t>Le gâteau du président - VOST + CM2</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr"/>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>VE</t>
         </is>
       </c>
       <c r="D18" s="5" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>14h</t>
+          <t>21h</t>
         </is>
       </c>
     </row>
     <row r="19" ht="40" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Maspalomas - VOST</t>
+          <t>Les toutes petites créatures 2</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr"/>
@@ -842,18 +842,18 @@
         </is>
       </c>
       <c r="D19" s="5" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>16h</t>
+          <t>17h</t>
         </is>
       </c>
     </row>
     <row r="20" ht="40" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>La danse des renards</t>
+          <t>Nuages flottants - VOST</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr"/>
@@ -863,18 +863,18 @@
         </is>
       </c>
       <c r="D20" s="5" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>18h15</t>
+          <t>18h</t>
         </is>
       </c>
     </row>
     <row r="21" ht="40" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>Le garçon qui faisait danser les  collines - VOST</t>
+          <t>Palestine 36</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr"/>
@@ -884,18 +884,18 @@
         </is>
       </c>
       <c r="D21" s="5" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>21h15</t>
+          <t>21h</t>
         </is>
       </c>
     </row>
     <row r="22" ht="40" customHeight="1">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>Affection, affection</t>
+          <t>Le chant des forêts</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr"/>
@@ -905,18 +905,18 @@
         </is>
       </c>
       <c r="D22" s="5" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>11h</t>
+          <t>15h</t>
         </is>
       </c>
     </row>
     <row r="23" ht="40" customHeight="1">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>Un jour avec mon père - VOST</t>
+          <t>Gourou</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr"/>
@@ -926,39 +926,39 @@
         </is>
       </c>
       <c r="D23" s="5" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>15h</t>
+          <t>17h</t>
         </is>
       </c>
     </row>
     <row r="24" ht="40" customHeight="1">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>La maison des femmes</t>
+          <t>Les légendaires</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr"/>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>DI</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="D24" s="5" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>17h</t>
+          <t>16h</t>
         </is>
       </c>
     </row>
     <row r="25" ht="40" customHeight="1">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>Piro Piro</t>
+          <t>Soulèvements</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr"/>
@@ -968,72 +968,429 @@
         </is>
       </c>
       <c r="D25" s="5" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>9h30</t>
+          <t>21h</t>
         </is>
       </c>
     </row>
     <row r="26" ht="40" customHeight="1">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>Le mécano de la générale</t>
+          <t>Les dimanches - VOST</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr"/>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>ME</t>
         </is>
       </c>
       <c r="D26" s="5" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>14h30</t>
+          <t>21h</t>
         </is>
       </c>
     </row>
     <row r="27" ht="40" customHeight="1">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>CM2 - Réel</t>
+          <t>Les toutes petites créatures 2</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr"/>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>JE</t>
         </is>
       </c>
       <c r="D27" s="5" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>21h</t>
+          <t>17h</t>
         </is>
       </c>
     </row>
     <row r="28" ht="40" customHeight="1">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>L'affaire Bojarski + CM2</t>
+          <t>Nurenberg - VOST</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr"/>
       <c r="C28" s="5" t="inlineStr">
         <is>
+          <t>JE</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>21h</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="40" customHeight="1">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>Marsupilami JP famille</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr"/>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>VE</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>15h</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="40" customHeight="1">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Aucun autre choix - VOST</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr"/>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>VE</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>21h</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="40" customHeight="1">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>Biscuit le chien fantastique</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr"/>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>16h</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="40" customHeight="1">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>Hamnet - VOST</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr"/>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>18h</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="40" customHeight="1">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>A pied d'œuvre</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr"/>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>21h</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="40" customHeight="1">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>Les légendaires</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr"/>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>DI</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>15h</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="40" customHeight="1">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>Promis le ciel</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr"/>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>DI</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>17h</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="40" customHeight="1">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Gourou</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr"/>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
           <t>MA</t>
         </is>
       </c>
-      <c r="D28" s="5" t="n">
+      <c r="D36" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>21h</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="40" customHeight="1">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Les voyages de Tereza - VOST</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr"/>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>ME</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>21h</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="40" customHeight="1">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>Dreams - VOST</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr"/>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>JE</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>21h</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="40" customHeight="1">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>Lol 2.0</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr"/>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>VE</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>21h</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="40" customHeight="1">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Super Charlie</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr"/>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>16h</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="40" customHeight="1">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>Abel - VOST</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr"/>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>18h</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="40" customHeight="1">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Maigret et le mort amoureux</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr"/>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>21h</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="40" customHeight="1">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Tafiti</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr"/>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>DI</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>15h</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="40" customHeight="1">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Les enfants de la Résistance</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr"/>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>DI</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>17h</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="40" customHeight="1">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>Le mystérieux regard du flamant rose - VOST</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr"/>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="E28" s="5" t="inlineStr">
+      <c r="E45" s="5" t="inlineStr">
         <is>
           <t>21h</t>
         </is>
